--- a/Planilha_Mestre_Panorama_v6.3.xlsx
+++ b/Planilha_Mestre_Panorama_v6.3.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incorporadoras" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Empreendimentos'!$A$5:$X$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Empreendimentos'!$A$5:$X$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Incorporadoras'!$A$5:$O$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X52"/>
+  <dimension ref="A1:X53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2319,32 +2319,32 @@
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Monteplan</t>
+          <t>Lua Nova</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Renaissance Conceito</t>
+          <t>Golden Green Beach</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Rua Caxuxa, S/N, Renascença II, São Luís - MA</t>
+          <t>Acesso pela Avenida dos Holandeses, São Luís - MA</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Renascença II</t>
+          <t>Calhau</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Loteamento</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Médio</t>
         </is>
       </c>
       <c r="G22" s="6" t="n"/>
@@ -2358,22 +2358,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
+      <c r="J22" s="8" t="n">
+        <v>453</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>682</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>567.5</v>
+      </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>3D</t>
-        </is>
-      </c>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>2650000</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>6211.453744493392</v>
+      </c>
       <c r="Q22" s="9" t="n"/>
       <c r="R22" s="10" t="n"/>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>book</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -2383,54 +2395,54 @@
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>book</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>https://monteplanengenharia.com.br/empreendimentos/renaissance-conceito/</t>
+          <t>https://construtoraluanova.com.br</t>
         </is>
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 3Q. Alto padrão Renascença II (Loteamento Boa Vista). Dois torres, lazer completo.</t>
+          <t>LOTEAMENTO DE LUXO. Projeto Golden Green Beach (GGB) — bairro de luxo planejado, acesso pela Av. dos Holandeses. Lote 41: 453 m² R$ 2,65M (R$ 5.850/m² terreno). Lote 42: 682 m² R$ 4,40M (R$ 6.452/m² terreno). Em obra. Áreas comuns: piscina coberta aquecida, sauna a vapor, heliponto com acesso por escada e elevador, estacionamento 30 carros, área administrativa. Projeto arquitetônico das áreas comuns: Marcelo Franco. Urbanismo: SA Urbanismo. Referências de luxo (book): Porto Frade RJ, Fazenda Boa Vista SP, Quinta da Baroneza SP. Bairro a confirmar (Calhau ou São Marcos pela posição na Av. Holandeses). ATENÇÃO: R$/m² em loteamento é TERRENO, não construído — não compara diretamente com aptos.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Monteplan</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Villagio Treviso</t>
+          <t>Renaissance Conceito</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, São Luís - MA</t>
+          <t>Rua Caxuxa, S/N, Renascença II, São Luís - MA</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>São Luís</t>
+          <t>Renascença II</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G23" s="12" t="n"/>
@@ -2449,7 +2461,7 @@
       <c r="L23" s="14" t="n"/>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>3D</t>
         </is>
       </c>
       <c r="N23" s="15" t="n"/>
@@ -2459,14 +2471,14 @@
       <c r="R23" s="16" t="n"/>
       <c r="S23" s="12" t="inlineStr">
         <is>
+          <t>site_oficial</t>
+        </is>
+      </c>
+      <c r="T23" s="12" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="T23" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="U23" s="12" t="inlineStr">
         <is>
           <t>site_oficial</t>
@@ -2474,7 +2486,7 @@
       </c>
       <c r="V23" s="12" t="inlineStr">
         <is>
-          <t>https://trevisoengenharia.com.br</t>
+          <t>https://monteplanengenharia.com.br/empreendimentos/renaissance-conceito/</t>
         </is>
       </c>
       <c r="W23" s="12" t="inlineStr">
@@ -2484,101 +2496,83 @@
       </c>
       <c r="X23" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: Terrenos em condomínio. Condomínio de terrenos (loteamento fechado). Divulgação ativa abr/2026. Sem tabela pública mapeada.</t>
+          <t>Tipologia detalhada: 3Q. Alto padrão Renascença II (Loteamento Boa Vista). Dois torres, lazer completo.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Studio Design 7 Península</t>
+          <t>Villagio Treviso</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, São Luís - MA</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>São Luís</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Luxo</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>125</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>04/2025 ⚠ T-36</t>
+          <t>06/2025 ⚠ T-36</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>04/2028</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="K24" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>53.5</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>Studio; 1D</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>710000</v>
-      </c>
-      <c r="O24" s="9" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="P24" s="9" t="n">
-        <v>15981.30841121495</v>
-      </c>
-      <c r="Q24" s="9" t="n">
-        <v>106875000</v>
-      </c>
-      <c r="R24" s="10" t="n">
-        <v>0.736</v>
-      </c>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="10" t="n"/>
       <c r="S24" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
         <is>
-          <t>estimativa_T-36</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://trevisoengenharia.com.br</t>
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr">
@@ -2588,29 +2582,29 @@
       </c>
       <c r="X24" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: Studio / 1Q. 33 de 125 aptos à venda. ≈74% vendido em ~18 meses. Forte velocidade em compactos.</t>
+          <t>Tipologia detalhada: Terrenos em condomínio. Condomínio de terrenos (loteamento fechado). Divulgação ativa abr/2026. Sem tabela pública mapeada.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Hiali</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Le Noir</t>
+          <t>Studio Design 7 Península</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Rua Osires, 05, Renascença II, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Renascença II</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -2620,95 +2614,101 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G25" s="12" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>04/2025 ⚠ T-36</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>12/2027</t>
+          <t>04/2028</t>
         </is>
       </c>
       <c r="J25" s="14" t="n">
-        <v>49.74</v>
+        <v>43</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>62.62</v>
+        <v>64</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>56.18</v>
+        <v>53.5</v>
       </c>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>Studio; 1D; 2D</t>
+          <t>Studio; 1D</t>
         </is>
       </c>
       <c r="N25" s="15" t="n">
         <v>710000</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>870000</v>
+        <v>1000000</v>
       </c>
       <c r="P25" s="15" t="n">
-        <v>14061.94375222499</v>
+        <v>15981.30841121495</v>
       </c>
       <c r="Q25" s="15" t="n">
-        <v>19750000</v>
-      </c>
-      <c r="R25" s="16" t="n"/>
+        <v>106875000</v>
+      </c>
+      <c r="R25" s="16" t="n">
+        <v>0.736</v>
+      </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U25" s="12" t="inlineStr">
         <is>
-          <t>memorial</t>
-        </is>
-      </c>
-      <c r="V25" s="12" t="inlineStr"/>
+          <t>estimativa_T-36</t>
+        </is>
+      </c>
+      <c r="V25" s="12" t="inlineStr">
+        <is>
+          <t>https://www.delman.com.br</t>
+        </is>
+      </c>
       <c r="W25" s="12" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="X25" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: Studios e 1-2 dorm (compactos premium). Parceria Hiali + Silveira Inc. Compactos premium: 49,74 / 58,91 / 62,62 m². 5 pavimentos tipo × 5 aptos/andar = ~25 unidades. Entrega DEZ/2027. Ticket R$ 710-870k. R$/m² méd R$ 13.810. Memorial R.09/25.101 registrado 17/04/2025 no 1º RI São Luís. Foco em mercado jovem / investidor. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: Studio / 1Q. 33 de 125 aptos à venda. ≈74% vendido em ~18 meses. Forte velocidade em compactos.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Alfa Engenharia</t>
+          <t>Hiali</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Giardino Residenza Torre Fiore</t>
+          <t>Le Noir</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Ponta do Farol, São Luís - MA</t>
+          <t>Rua Osires, 05, Renascença II, São Luís - MA</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Ponta do Farol</t>
+          <t>Renascença II</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -2718,59 +2718,57 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Luxo</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>12/2029</t>
+          <t>12/2027</t>
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>110.77</v>
+        <v>49.74</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>128.37</v>
+        <v>62.62</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>119.57</v>
+        <v>56.18</v>
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>3D</t>
+          <t>Studio; 1D; 2D</t>
         </is>
       </c>
       <c r="N26" s="9" t="n">
-        <v>1838492</v>
+        <v>710000</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>2032939</v>
+        <v>870000</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>16188.97298653509</v>
+        <v>14061.94375222499</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>87107197.5</v>
-      </c>
-      <c r="R26" s="10" t="n">
-        <v>0.8666666666666667</v>
-      </c>
+        <v>19750000</v>
+      </c>
+      <c r="R26" s="10" t="n"/>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -2778,19 +2776,15 @@
           <t>memorial</t>
         </is>
       </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/alfaengenhariama/</t>
-        </is>
-      </c>
+      <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 2 suítes + 2 semi-suítes OU 3 suítes, varanda, lavabo, 3 vagas, depósito. Torre NORTE do Giardino. 15 pav × 3 un = 45 unidades. 3 tipologias: 127,30 / 128,37 / 110,77 m². Tabela MAR/2026: 6 unidades disponíveis (1001/701/201/101 da coluna 127m², 102 da coluna 128m², 1403 da coluna 110m²) = ~13% estoque, 87% VENDIDO → Últimas unidades. Entrega DEZ/29. Memorial R.06/56.931 - 1º RI SL. Endereço Alfa: Rua Peixe Pedra, Qd 12 lote 04, Calhau.</t>
+          <t>Tipologia detalhada: Studios e 1-2 dorm (compactos premium). Parceria Hiali + Silveira Inc. Compactos premium: 49,74 / 58,91 / 62,62 m². 5 pavimentos tipo × 5 aptos/andar = ~25 unidades. Entrega DEZ/2027. Ticket R$ 710-870k. R$/m² méd R$ 13.810. Memorial R.09/25.101 registrado 17/04/2025 no 1º RI São Luís. Foco em mercado jovem / investidor. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2796,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Giardino Residenza Torre Luce</t>
+          <t>Giardino Residenza Torre Fiore</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -2826,7 +2820,7 @@
         </is>
       </c>
       <c r="G27" s="12" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
@@ -2839,13 +2833,13 @@
         </is>
       </c>
       <c r="J27" s="14" t="n">
-        <v>93.18000000000001</v>
+        <v>110.77</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>101.31</v>
+        <v>128.37</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>97.245</v>
+        <v>119.57</v>
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
@@ -2853,19 +2847,19 @@
         </is>
       </c>
       <c r="N27" s="15" t="n">
-        <v>1442168</v>
+        <v>1838492</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>1595303</v>
+        <v>2032939</v>
       </c>
       <c r="P27" s="15" t="n">
-        <v>15617.62044321045</v>
+        <v>16188.97298653509</v>
       </c>
       <c r="Q27" s="15" t="n">
-        <v>91124130</v>
+        <v>87107197.5</v>
       </c>
       <c r="R27" s="16" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
@@ -2894,29 +2888,29 @@
       </c>
       <c r="X27" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 3 suítes, varanda, lavabo, 2 vagas, depósito. Torre SUL do Giardino. 15 pav × 4 un = 60 unidades. 4 tipologias: 99,08 / 101,31 / 93,18 / 93,62 m². Tabela MAR/2026: 5 unidades disponíveis (701/101 col 99m², 1502/1402 col 101m², 104 col 93m²) = ~8% estoque, 92% VENDIDO → Últimas unidades. CORREÇÃO v5.1: dorms = 3 suítes (descrição da tabela MAR/26), antes constava '2 suítes/1 suíte' incorretamente. 2 vagas + 1 depósito. Mais acessível que Torre Fiore. Entrega DEZ/29. Memorial R.06/56.931 - 1º RI SL.</t>
+          <t>Tipologia detalhada: 2 suítes + 2 semi-suítes OU 3 suítes, varanda, lavabo, 3 vagas, depósito. Torre NORTE do Giardino. 15 pav × 3 un = 45 unidades. 3 tipologias: 127,30 / 128,37 / 110,77 m². Tabela MAR/2026: 6 unidades disponíveis (1001/701/201/101 da coluna 127m², 102 da coluna 128m², 1403 da coluna 110m²) = ~13% estoque, 87% VENDIDO → Últimas unidades. Entrega DEZ/29. Memorial R.06/56.931 - 1º RI SL. Endereço Alfa: Rua Peixe Pedra, Qd 12 lote 04, Calhau.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Alfa Engenharia</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Vernazza Torre Norte</t>
+          <t>Giardino Residenza Torre Luce</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Ponta do Farol, São Luís - MA</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Ponta do Farol</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -2930,7 +2924,7 @@
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
@@ -2943,33 +2937,33 @@
         </is>
       </c>
       <c r="J28" s="8" t="n">
-        <v>130</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>130</v>
+        <v>101.31</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>130</v>
+        <v>97.245</v>
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3D</t>
         </is>
       </c>
       <c r="N28" s="9" t="n">
-        <v>1820000</v>
+        <v>1442168</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>2235000</v>
+        <v>1595303</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>15596.15384615385</v>
+        <v>15617.62044321045</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>243300000</v>
+        <v>91124130</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
@@ -2983,22 +2977,22 @@
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
-          <t>informado</t>
+          <t>memorial</t>
         </is>
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>https://www.treviso.com.br</t>
+          <t>https://www.instagram.com/alfaengenhariama/</t>
         </is>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="X28" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: Aptos 130 m² — Leste/Sul/Norte. Lançamento 02/2025 informado pelo Rafael (fonte externa confiável). Tabela de 02/2026 arquivada confirma vendas ativas naquela data, mas não é data de lançamento — aguarda book ou memorial para data confiável. Torre Norte: 37 unid, área 130 m², ticket R$ 1,82-2,24M (méd R$ 2,02M). R$/m² méd R$ 15.524. VGV listado R$ 74,8M. Entrega 12/2029. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: 3 suítes, varanda, lavabo, 2 vagas, depósito. Torre SUL do Giardino. 15 pav × 4 un = 60 unidades. 4 tipologias: 99,08 / 101,31 / 93,18 / 93,62 m². Tabela MAR/2026: 5 unidades disponíveis (701/101 col 99m², 1502/1402 col 101m², 104 col 93m²) = ~8% estoque, 92% VENDIDO → Últimas unidades. CORREÇÃO v5.1: dorms = 3 suítes (descrição da tabela MAR/26), antes constava '2 suítes/1 suíte' incorretamente. 2 vagas + 1 depósito. Mais acessível que Torre Fiore. Entrega DEZ/29. Memorial R.06/56.931 - 1º RI SL.</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3004,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Vernazza Torre Sul</t>
+          <t>Vernazza Torre Norte</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -3033,7 +3027,9 @@
           <t>Luxo</t>
         </is>
       </c>
-      <c r="G29" s="12" t="n"/>
+      <c r="G29" s="12" t="n">
+        <v>120</v>
+      </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
           <t>02/2025</t>
@@ -3045,13 +3041,13 @@
         </is>
       </c>
       <c r="J29" s="14" t="n">
-        <v>87.98</v>
+        <v>130</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>90.09999999999999</v>
+        <v>130</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>89.03999999999999</v>
+        <v>130</v>
       </c>
       <c r="M29" s="13" t="inlineStr">
         <is>
@@ -3059,24 +3055,28 @@
         </is>
       </c>
       <c r="N29" s="15" t="n">
-        <v>1277000</v>
+        <v>1820000</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>1586000</v>
+        <v>2235000</v>
       </c>
       <c r="P29" s="15" t="n">
-        <v>16077.04402515723</v>
-      </c>
-      <c r="Q29" s="15" t="n"/>
-      <c r="R29" s="16" t="n"/>
+        <v>15596.15384615385</v>
+      </c>
+      <c r="Q29" s="15" t="n">
+        <v>243300000</v>
+      </c>
+      <c r="R29" s="16" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="T29" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U29" s="12" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.treviso.com.br</t>
         </is>
       </c>
       <c r="W29" s="12" t="inlineStr">
@@ -3096,29 +3096,29 @@
       </c>
       <c r="X29" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 87,98 e 90,10 m² (Norte/Sul). Lançamento 02/2025 informado pelo Rafael. 26 unid listadas, área 87,98/90,10 m². Ticket R$ 1,28-1,59M (méd R$ 1,40M). R$/m² pond R$ 15.600 (faixa R$ 14,2-17,6k). VGV listado R$ 36,3M. Entrega 12/2029. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: Aptos 130 m² — Leste/Sul/Norte. Lançamento 02/2025 informado pelo Rafael (fonte externa confiável). Tabela de 02/2026 arquivada confirma vendas ativas naquela data, mas não é data de lançamento — aguarda book ou memorial para data confiável. Torre Norte: 37 unid, área 130 m², ticket R$ 1,82-2,24M (méd R$ 2,02M). R$/m² méd R$ 15.524. VGV listado R$ 74,8M. Entrega 12/2029. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Mota Machado</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Reserva São Marcos</t>
+          <t>Vernazza Torre Sul</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Calhau, São Luís - MA</t>
+          <t>Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Calhau</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -3128,83 +3128,95 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>01/2025</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
+          <t>12/2029</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>89.03999999999999</v>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="9" t="n"/>
-      <c r="O30" s="9" t="n"/>
-      <c r="P30" s="9" t="n"/>
+      <c r="N30" s="9" t="n">
+        <v>1277000</v>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>1586000</v>
+      </c>
+      <c r="P30" s="9" t="n">
+        <v>16077.04402515723</v>
+      </c>
       <c r="Q30" s="9" t="n"/>
       <c r="R30" s="10" t="n"/>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>informado</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>https://www.motamachado.com.br</t>
+          <t>—</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="X30" s="7" t="inlineStr">
         <is>
-          <t>Obras iniciadas 09/2025. Empresa de Fortaleza expandindo no Nordeste. SEM material local.</t>
+          <t>Tipologia detalhada: 87,98 e 90,10 m² (Norte/Sul). Lançamento 02/2025 informado pelo Rafael. 26 unid listadas, área 87,98/90,10 m². Ticket R$ 1,28-1,59M (méd R$ 1,40M). R$/m² pond R$ 15.600 (faixa R$ 14,2-17,6k). VGV listado R$ 36,3M. Entrega 12/2029. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Mota Machado</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Sky Residence</t>
+          <t>Reserva São Marcos</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, Calhau, São Luís - MA</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Calhau</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -3214,69 +3226,51 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Luxo</t>
-        </is>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>12</v>
-      </c>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="n"/>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>09/2024 ⚠ T-36</t>
+          <t>01/2025</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>09/2027</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>246.69</v>
-      </c>
-      <c r="K31" s="14" t="n">
-        <v>246.69</v>
-      </c>
-      <c r="L31" s="14" t="n">
-        <v>246.69</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="14" t="n"/>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>4D</t>
-        </is>
-      </c>
-      <c r="N31" s="15" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="O31" s="15" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="P31" s="15" t="n">
-        <v>19052.25181401759</v>
-      </c>
-      <c r="Q31" s="15" t="n">
-        <v>56400000</v>
-      </c>
-      <c r="R31" s="16" t="n">
-        <v>0.9166666666666666</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="15" t="n"/>
+      <c r="O31" s="15" t="n"/>
+      <c r="P31" s="15" t="n"/>
+      <c r="Q31" s="15" t="n"/>
+      <c r="R31" s="16" t="n"/>
       <c r="S31" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="T31" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U31" s="12" t="inlineStr">
         <is>
-          <t>estimativa_T-36</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="V31" s="12" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://www.motamachado.com.br</t>
         </is>
       </c>
       <c r="W31" s="12" t="inlineStr">
@@ -3286,29 +3280,29 @@
       </c>
       <c r="X31" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 4 suítes. Prédio pequeno (12 aptos). 1 à venda. ≈92% vendido.</t>
+          <t>Obras iniciadas 09/2025. Empresa de Fortaleza expandindo no Nordeste. SEM material local.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Mota Machado</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Al Mare Tirreno</t>
+          <t>Sky Residence</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Av. dos Holandeses, Qd 9 Lt 9, São Marcos, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>São Marcos</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -3318,28 +3312,30 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="n"/>
+          <t>Luxo</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>12</v>
+      </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>08/2024</t>
+          <t>09/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Pronto</t>
+          <t>09/2027</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
-        <v>215</v>
+        <v>246.69</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>215</v>
+        <v>246.69</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>215</v>
+        <v>246.69</v>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
@@ -3347,44 +3343,48 @@
         </is>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3025856</v>
+        <v>4700000</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>3120721</v>
+        <v>4700000</v>
       </c>
       <c r="P32" s="9" t="n">
-        <v>14294.36511627907</v>
-      </c>
-      <c r="Q32" s="9" t="n"/>
-      <c r="R32" s="10" t="n"/>
+        <v>19052.25181401759</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>56400000</v>
+      </c>
+      <c r="R32" s="10" t="n">
+        <v>0.9166666666666666</v>
+      </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>estimativa_T-36</t>
         </is>
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>https://motamachado.com.br</t>
+          <t>https://www.delman.com.br</t>
         </is>
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 4 suítes, 3 vagas. Torre A 'Tirreno' da Mota Machado Collection. Imóvel PRONTO. 215 m², 4 suítes, 3 vagas. Apts 102, 201, 202 listados. Ticket R$ 3,02-3,12M. R$/m² méd R$ 14.293. Av. dos Holandeses / São Marcos. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: 4 suítes. Prédio pequeno (12 aptos). 1 à venda. ≈92% vendido.</t>
         </is>
       </c>
     </row>
@@ -3396,17 +3396,17 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Entre Rios</t>
+          <t>Al Mare Tirreno</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Rua dos Bicudos, S/N, Qd. XIV-A Lote 02, Renascença, São Luís - MA</t>
+          <t>Av. dos Holandeses, Qd 9 Lt 9, São Marcos, São Luís - MA</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Renascença</t>
+          <t>São Marcos</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Luxo</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G33" s="12" t="n"/>
@@ -3427,31 +3427,31 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pronto</t>
         </is>
       </c>
       <c r="J33" s="14" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="K33" s="14" t="n">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>3D</t>
+          <t>4D</t>
         </is>
       </c>
       <c r="N33" s="15" t="n">
-        <v>1732000</v>
+        <v>3025856</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>2720000</v>
+        <v>3120721</v>
       </c>
       <c r="P33" s="15" t="n">
-        <v>15787.23404255319</v>
+        <v>14294.36511627907</v>
       </c>
       <c r="Q33" s="15" t="n"/>
       <c r="R33" s="16" t="n"/>
@@ -3482,29 +3482,29 @@
       </c>
       <c r="X33" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 3 suítes (1 master). 3 tipologias (125 / 146,82 / 156,94 m²). 2 torres x 15 pav. Tab ABR/26: 15 unid, VGV R$ 32,3M. Ticket R$ 1,73–2,72M (méd R$ 2,15M). R$/m² pond R$ 15.162 (faixa R$ 13,9k–17,3k). Rua dos Bicudos, Renascença. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: 4 suítes, 3 vagas. Torre A 'Tirreno' da Mota Machado Collection. Imóvel PRONTO. 215 m², 4 suítes, 3 vagas. Apts 102, 201, 202 listados. Ticket R$ 3,02-3,12M. R$/m² méd R$ 14.293. Av. dos Holandeses / São Marcos. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Alfa Engenharia</t>
+          <t>Mota Machado</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Connect Península</t>
+          <t>Entre Rios</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Rua dos Bicudos, S/N, Qd. XIV-A Lote 02, Renascença, São Luís - MA</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Renascença</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -3514,13 +3514,13 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>07/2024</t>
+          <t>08/2024</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
@@ -3528,47 +3528,59 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
-      <c r="L34" s="8" t="n"/>
+      <c r="J34" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="K34" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>141</v>
+      </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="9" t="n"/>
-      <c r="O34" s="9" t="n"/>
-      <c r="P34" s="9" t="n"/>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>1732000</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>2720000</v>
+      </c>
+      <c r="P34" s="9" t="n">
+        <v>15787.23404255319</v>
+      </c>
       <c r="Q34" s="9" t="n"/>
       <c r="R34" s="10" t="n"/>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>book</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>https://www.alfaengenharia.com.br</t>
+          <t>https://motamachado.com.br</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="X34" s="7" t="inlineStr">
         <is>
-          <t>Tipologia a confirmar em book/site/Instagram. Tecnologia Housi (gestão de locação) NÃO determina tipologia — descrição anterior corrigida. Sem tabela comercial pública.</t>
+          <t>Tipologia detalhada: 3 suítes (1 master). 3 tipologias (125 / 146,82 / 156,94 m²). 2 torres x 15 pav. Tab ABR/26: 15 unid, VGV R$ 32,3M. Ticket R$ 1,73–2,72M (méd R$ 2,15M). R$/m² pond R$ 15.162 (faixa R$ 13,9k–17,3k). Rua dos Bicudos, Renascença. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3592,7 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Legacy Residence</t>
+          <t>Connect Península</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -3600,7 +3612,7 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Luxo</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G35" s="12" t="n"/>
@@ -3611,7 +3623,7 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>10/2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" s="14" t="n"/>
@@ -3619,7 +3631,7 @@
       <c r="L35" s="14" t="n"/>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>4D</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="15" t="n"/>
@@ -3639,7 +3651,7 @@
       </c>
       <c r="U35" s="12" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="V35" s="12" t="inlineStr">
@@ -3654,64 +3666,58 @@
       </c>
       <c r="X35" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 4 suítes. 13 opções de lazer, elevador privativo. Book local (375MB) + site oficial. Sem ticket público.</t>
+          <t>Tipologia a confirmar em book/site/Instagram. Tecnologia Housi (gestão de locação) NÃO determina tipologia — descrição anterior corrigida. Sem tabela comercial pública.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Castelucci</t>
+          <t>Alfa Engenharia</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Villa di Carpi</t>
+          <t>Legacy Residence</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Cohatrac, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Cohatrac</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>06/2024 ⚠ T-36</t>
+          <t>07/2024</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="K36" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>50.5</v>
-      </c>
+          <t>10/2027</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>2D</t>
+          <t>4D</t>
         </is>
       </c>
       <c r="N36" s="9" t="n"/>
@@ -3721,7 +3727,7 @@
       <c r="R36" s="10" t="n"/>
       <c r="S36" s="6" t="inlineStr">
         <is>
-          <t>agregador</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
@@ -3731,12 +3737,12 @@
       </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>https://construtoracastelucci.com.br</t>
+          <t>https://www.alfaengenharia.com.br</t>
         </is>
       </c>
       <c r="W36" s="6" t="inlineStr">
@@ -3746,29 +3752,29 @@
       </c>
       <c r="X36" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 2Q. Compactos 49-52m², 2Q. Público Cohatrac/médio. Instagram @construtoracastelucci anunciou como lançamento; preço não divulgado.</t>
+          <t>Tipologia detalhada: 4 suítes. 13 opções de lazer, elevador privativo. Book local (375MB) + site oficial. Sem ticket público.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>DOM Incorporação</t>
+          <t>Castelucci</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Dom José</t>
+          <t>Villa di Carpi</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>FQV9+JJ Jardim Eldorado, São Luís - MA</t>
+          <t>Endereço não localizado, Cohatrac, São Luís - MA</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Jardim Eldorado</t>
+          <t>Cohatrac</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -3778,91 +3784,89 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>Médio-alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="12" t="n"/>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>06/2024</t>
+          <t>06/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" s="14" t="n">
-        <v>154.64</v>
+        <v>49</v>
       </c>
       <c r="K37" s="14" t="n">
-        <v>154.64</v>
+        <v>52</v>
       </c>
       <c r="L37" s="14" t="n">
-        <v>154.64</v>
+        <v>50.5</v>
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>4D</t>
-        </is>
-      </c>
-      <c r="N37" s="15" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="O37" s="15" t="n">
-        <v>1415000</v>
-      </c>
-      <c r="P37" s="15" t="n">
-        <v>9101.784790481119</v>
-      </c>
+          <t>2D</t>
+        </is>
+      </c>
+      <c r="N37" s="15" t="n"/>
+      <c r="O37" s="15" t="n"/>
+      <c r="P37" s="15" t="n"/>
       <c r="Q37" s="15" t="n"/>
       <c r="R37" s="16" t="n"/>
       <c r="S37" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>agregador</t>
         </is>
       </c>
       <c r="T37" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U37" s="12" t="inlineStr">
         <is>
-          <t>interno</t>
-        </is>
-      </c>
-      <c r="V37" s="12" t="inlineStr"/>
+          <t>site_oficial</t>
+        </is>
+      </c>
+      <c r="V37" s="12" t="inlineStr">
+        <is>
+          <t>https://construtoracastelucci.com.br</t>
+        </is>
+      </c>
       <c r="W37" s="12" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="X37" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: Casa 4+ dorm, alto padrão. Condomínio horizontal alto padrão. 1 ÚNICA tipologia: casa 154,64 m² construída. Terreno varia 170-181 m² conforme posição. Maioria das unidades VENDIDAS (14+ marcadas VENDIDA na tabela ABR/2026). Entrega 06/2027. Ticket ~R$ 1,4M → R$/m² construção ~R$ 9.150. CORREÇÃO v5.2: Área máx era 180,98 (terreno) — corrigida para 154,64 (construída). Convenção PADRAO §1: Tipo=Horizontal usa área construída.</t>
+          <t>Tipologia detalhada: 2Q. Compactos 49-52m², 2Q. Público Cohatrac/médio. Instagram @construtoracastelucci anunciou como lançamento; preço não divulgado.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Franere</t>
+          <t>DOM Incorporação</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Varandas Grand Park</t>
+          <t>Dom José</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, São Luís - MA</t>
+          <t>FQV9+JJ Jardim Eldorado, São Luís - MA</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>São Luís</t>
+          <t>Jardim Eldorado</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -3872,73 +3876,81 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Médio-alto</t>
         </is>
       </c>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>06/2024 ⚠ T-36</t>
+          <t>06/2024</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-      <c r="L38" s="8" t="n"/>
+          <t>06/2027</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>154.64</v>
+      </c>
+      <c r="K38" s="8" t="n">
+        <v>154.64</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>154.64</v>
+      </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N38" s="9" t="n"/>
-      <c r="O38" s="9" t="n"/>
-      <c r="P38" s="9" t="n"/>
+          <t>4D</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>1415000</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>9101.784790481119</v>
+      </c>
       <c r="Q38" s="9" t="n"/>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
-        </is>
-      </c>
-      <c r="V38" s="6" t="inlineStr">
-        <is>
-          <t>https://franere.com.br</t>
-        </is>
-      </c>
+          <t>interno</t>
+        </is>
+      </c>
+      <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="X38" s="7" t="inlineStr">
         <is>
-          <t>Franere ('Maior construtora do Maranhão', 40 anos). Série 'Gran Park' tem múltiplos módulos. IG @franereoficial_.</t>
+          <t>Tipologia detalhada: Casa 4+ dorm, alto padrão. Condomínio horizontal alto padrão. 1 ÚNICA tipologia: casa 154,64 m² construída. Terreno varia 170-181 m² conforme posição. Maioria das unidades VENDIDAS (14+ marcadas VENDIDA na tabela ABR/2026). Entrega 06/2027. Ticket ~R$ 1,4M → R$/m² construção ~R$ 9.150. CORREÇÃO v5.2: Área máx era 180,98 (terreno) — corrigida para 154,64 (construída). Convenção PADRAO §1: Tipo=Horizontal usa área construída.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>Lua Nova</t>
+          <t>Franere</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Villa Adagio</t>
+          <t>Varandas Grand Park</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -4002,7 +4014,7 @@
       </c>
       <c r="V39" s="12" t="inlineStr">
         <is>
-          <t>https://construtoraluanova.com.br</t>
+          <t>https://franere.com.br</t>
         </is>
       </c>
       <c r="W39" s="12" t="inlineStr">
@@ -4012,127 +4024,115 @@
       </c>
       <c r="X39" s="13" t="inlineStr">
         <is>
-          <t>Construtora Lua Nova desde 1985. IG @construtoraluanova. Detalhes tipologia/ticket a coletar via book.</t>
+          <t>Franere ('Maior construtora do Maranhão', 40 anos). Série 'Gran Park' tem múltiplos módulos. IG @franereoficial_.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Berg Engenharia</t>
+          <t>Lua Nova</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Monte Meru</t>
+          <t>Villa Adagio</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, São Luís - MA</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>São Luís</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>04/2024</t>
+          <t>06/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>04/2027</t>
-        </is>
-      </c>
-      <c r="J40" s="8" t="n">
-        <v>135.32</v>
-      </c>
-      <c r="K40" s="8" t="n">
-        <v>135.83</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>135.575</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
       <c r="M40" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N40" s="9" t="n">
-        <v>1932400</v>
-      </c>
-      <c r="O40" s="9" t="n">
-        <v>1944500</v>
-      </c>
-      <c r="P40" s="9" t="n">
-        <v>14297.99004241195</v>
-      </c>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="9" t="n"/>
       <c r="Q40" s="9" t="n"/>
       <c r="R40" s="10" t="n"/>
       <c r="S40" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>https://www.bergengenharia.com.br</t>
+          <t>https://construtoraluanova.com.br</t>
         </is>
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="X40" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: Aptos 135 m², 2-3 vagas. Tabela ABR/2026 (Berg Engenharia). 4 tipologias (1-4) com áreas similares 135,32 / 135,83 m². Lançamento 04/2024 estimado pela pasta. Conclusão: 30/04/2027 (T-36 perfeito). Tipo 3 (135,32m²): apto 103 disponível R$ 1.932.400. Tipo 4 (135,83m²): apto 104 disponível R$ 1.944.500, demais (204-1004) VENDIDOS = 9 vendidos no Tipo 4 → estoque concentrado em 1 unidade visível. Apto 704 tem 3 vagas (diferencial). Correção INCC. Histórico Berg: Montparnasse, Golden Tower, Peninsula Mall, Monte Olimpo, Monte Fuji.</t>
+          <t>Construtora Lua Nova desde 1985. IG @construtoraluanova. Detalhes tipologia/ticket a coletar via book.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="52" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Berg Engenharia</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Altos do São Francisco</t>
+          <t>Monte Meru</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>Bairro São Francisco, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>São Francisco</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -4145,96 +4145,92 @@
           <t>Alto</t>
         </is>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>26</v>
-      </c>
+      <c r="G41" s="12" t="n"/>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>01/2024 ⚠ T-36</t>
+          <t>04/2024</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>Pronto</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="J41" s="14" t="n">
-        <v>57.93</v>
+        <v>135.32</v>
       </c>
       <c r="K41" s="14" t="n">
-        <v>67.15000000000001</v>
+        <v>135.83</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>62.54000000000001</v>
+        <v>135.575</v>
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>2D; 3D</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="15" t="n">
-        <v>495800</v>
+        <v>1932400</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>761700</v>
+        <v>1944500</v>
       </c>
       <c r="P41" s="15" t="n">
-        <v>10053.56571794052</v>
-      </c>
-      <c r="Q41" s="15" t="n">
-        <v>16347500</v>
-      </c>
+        <v>14297.99004241195</v>
+      </c>
+      <c r="Q41" s="15" t="n"/>
       <c r="R41" s="16" t="n"/>
       <c r="S41" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="T41" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U41" s="12" t="inlineStr">
         <is>
-          <t>pendente</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="V41" s="12" t="inlineStr">
         <is>
-          <t>https://trevisoengenharia.com.br</t>
+          <t>https://www.bergengenharia.com.br</t>
         </is>
       </c>
       <c r="W41" s="12" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="X41" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 2-3Q (1 ou 2 vagas). IMÓVEL PRONTO. 26+ unid na tab ABR/26 (VGV R$ 15,8M). Tipos: 57,93 m² (1 vaga) e 67,15 m² (2 vagas). Ticket R$ 495k–762k (méd R$ 607k). R$/m² pond R$ 10.042. Estoque amplo. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: Aptos 135 m², 2-3 vagas. Tabela ABR/2026 (Berg Engenharia). 4 tipologias (1-4) com áreas similares 135,32 / 135,83 m². Lançamento 04/2024 estimado pela pasta. Conclusão: 30/04/2027 (T-36 perfeito). Tipo 3 (135,32m²): apto 103 disponível R$ 1.932.400. Tipo 4 (135,83m²): apto 104 disponível R$ 1.944.500, demais (204-1004) VENDIDOS = 9 vendidos no Tipo 4 → estoque concentrado em 1 unidade visível. Apto 704 tem 3 vagas (diferencial). Correção INCC. Histórico Berg: Montparnasse, Golden Tower, Peninsula Mall, Monte Olimpo, Monte Fuji.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>DOM Incorporação</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Edifício Dom Ricardo</t>
+          <t>Altos do São Francisco</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Rua dos Rouxinóis, 8, Jardim Renascença, São Luís - MA</t>
+          <t>Bairro São Francisco, São Luís - MA</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Jardim Renascença</t>
+          <t>São Francisco</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -4244,59 +4240,67 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="n"/>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>26</v>
+      </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>01/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pronto</t>
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>71</v>
+        <v>57.93</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>85</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>78</v>
+        <v>62.54000000000001</v>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
           <t>2D; 3D</t>
         </is>
       </c>
-      <c r="N42" s="9" t="n"/>
-      <c r="O42" s="9" t="n"/>
-      <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="9" t="n"/>
-      <c r="R42" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+      <c r="N42" s="9" t="n">
+        <v>495800</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>761700</v>
+      </c>
+      <c r="P42" s="9" t="n">
+        <v>10053.56571794052</v>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>16347500</v>
+      </c>
+      <c r="R42" s="10" t="n"/>
       <c r="S42" s="6" t="inlineStr">
         <is>
-          <t>agregador</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>agregador</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
         <is>
-          <t>interno</t>
+          <t>pendente</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>https://www.imeu.com.br/empreendimento/dom-ricardo-apartamentos-sao-luis-2-a-3-quartos-71-a-85-m/19044585-MIM</t>
+          <t>https://trevisoengenharia.com.br</t>
         </is>
       </c>
       <c r="W42" s="6" t="inlineStr">
@@ -4306,29 +4310,29 @@
       </c>
       <c r="X42" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 2-3Q. DOM Incorporação com MB Engenharia como sócia (empreendimento conjunto). Lançamento 12/2023 confirmado internamente. Próximo à Praça da Lagoa (Foguete). 'Sucesso de vendas, 6 unidades disponíveis' (IG jan/2025). Estoque estimado ≤6%. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: 2-3Q (1 ou 2 vagas). IMÓVEL PRONTO. 26+ unid na tab ABR/26 (VGV R$ 15,8M). Tipos: 57,93 m² (1 vaga) e 67,15 m² (2 vagas). Ticket R$ 495k–762k (méd R$ 607k). R$/m² pond R$ 10.042. Estoque amplo. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="43" ht="52" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>Alfa Engenharia</t>
+          <t>DOM Incorporação</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>LIV Residence</t>
+          <t>Edifício Dom Ricardo</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Rua Aziz Heluy, S/N, Ponta d'Areia, São Luís - MA</t>
+          <t>Rua dos Rouxinóis, 8, Jardim Renascença, São Luís - MA</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Jardim Renascença</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -4338,13 +4342,13 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="12" t="n"/>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>07/2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
@@ -4352,64 +4356,72 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J43" s="14" t="n"/>
-      <c r="K43" s="14" t="n"/>
-      <c r="L43" s="14" t="n"/>
+      <c r="J43" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>3D</t>
+          <t>2D; 3D</t>
         </is>
       </c>
       <c r="N43" s="15" t="n"/>
       <c r="O43" s="15" t="n"/>
       <c r="P43" s="15" t="n"/>
       <c r="Q43" s="15" t="n"/>
-      <c r="R43" s="16" t="n"/>
+      <c r="R43" s="16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="S43" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>agregador</t>
         </is>
       </c>
       <c r="T43" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>agregador</t>
         </is>
       </c>
       <c r="U43" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>interno</t>
         </is>
       </c>
       <c r="V43" s="12" t="inlineStr">
         <is>
-          <t>https://www.alfaengenharia.com.br</t>
+          <t>https://www.imeu.com.br/empreendimento/dom-ricardo-apartamentos-sao-luis-2-a-3-quartos-71-a-85-m/19044585-MIM</t>
         </is>
       </c>
       <c r="W43" s="12" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="X43" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 3 suítes. 1º Housi do MA. Book local + site Alfa. Sem tabela comercial.</t>
+          <t>Tipologia detalhada: 2-3Q. DOM Incorporação com MB Engenharia como sócia (empreendimento conjunto). Lançamento 12/2023 confirmado internamente. Próximo à Praça da Lagoa (Foguete). 'Sucesso de vendas, 6 unidades disponíveis' (IG jan/2025). Estoque estimado ≤6%. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="44" ht="52" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Alfa Engenharia</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Azimuth</t>
+          <t>LIV Residence</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Rua Aziz Heluy, S/N, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -4424,12 +4436,10 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Luxo</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>30</v>
-      </c>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n"/>
       <c r="H44" s="6" t="inlineStr">
         <is>
           <t>07/2023</t>
@@ -4437,56 +4447,40 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>10/2026</t>
-        </is>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>196.62</v>
-      </c>
-      <c r="K44" s="8" t="n">
-        <v>196.62</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>196.62</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="8" t="n"/>
       <c r="M44" s="7" t="inlineStr">
         <is>
           <t>3D</t>
         </is>
       </c>
-      <c r="N44" s="9" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="O44" s="9" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="P44" s="9" t="n">
-        <v>18309.4293561184</v>
-      </c>
-      <c r="Q44" s="9" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="R44" s="10" t="n">
-        <v>0.9666666666666667</v>
-      </c>
+      <c r="N44" s="9" t="n"/>
+      <c r="O44" s="9" t="n"/>
+      <c r="P44" s="9" t="n"/>
+      <c r="Q44" s="9" t="n"/>
+      <c r="R44" s="10" t="n"/>
       <c r="S44" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="T44" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://www.alfaengenharia.com.br</t>
         </is>
       </c>
       <c r="W44" s="6" t="inlineStr">
@@ -4496,60 +4490,62 @@
       </c>
       <c r="X44" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 3 suítes. Tabela 04/2026: 1 apto (901) de 30. ≈97% vendido. Lançamento confirmado 2023 pela imprensa.</t>
+          <t>Tipologia detalhada: 3 suítes. 1º Housi do MA. Book local + site Alfa. Sem tabela comercial.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="52" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>DOM Incorporação</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Dom Antônio</t>
+          <t>Azimuth</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Jardim Eldorado (Turú), São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Jardim Eldorado</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="n"/>
+          <t>Luxo</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>30</v>
+      </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>06/2023</t>
+          <t>07/2023</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="J45" s="14" t="n">
-        <v>136</v>
+        <v>196.62</v>
       </c>
       <c r="K45" s="14" t="n">
-        <v>136</v>
+        <v>196.62</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>136</v>
+        <v>196.62</v>
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
@@ -4557,82 +4553,86 @@
         </is>
       </c>
       <c r="N45" s="15" t="n">
-        <v>906870</v>
+        <v>3600000</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>906870</v>
+        <v>3600000</v>
       </c>
       <c r="P45" s="15" t="n">
-        <v>6668.161764705882</v>
-      </c>
-      <c r="Q45" s="15" t="n"/>
-      <c r="R45" s="16" t="n"/>
+        <v>18309.4293561184</v>
+      </c>
+      <c r="Q45" s="15" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="R45" s="16" t="n">
+        <v>0.9666666666666667</v>
+      </c>
       <c r="S45" s="12" t="inlineStr">
         <is>
-          <t>agregador</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="T45" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U45" s="12" t="inlineStr">
         <is>
-          <t>interno</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="V45" s="12" t="inlineStr">
         <is>
-          <t>https://www.imovelnacidade.com/destaque/mb-construtora/</t>
+          <t>https://www.delman.com.br</t>
         </is>
       </c>
       <c r="W45" s="12" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="X45" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 3Q casas duplex. DOM Incorporação com MB Engenharia como sócia (empreendimento conjunto). Lançamento 06/2023 confirmado internamente. Casa duplex 3Q, 136m², R$906.870. Produto horizontal Eldorado/Turú. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: 3 suítes. Tabela 04/2026: 1 apto (901) de 30. ≈97% vendido. Lançamento confirmado 2023 pela imprensa.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="52" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Monteplan</t>
+          <t>DOM Incorporação</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Edifício Sanpaolo</t>
+          <t>Dom Antônio</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, São Luís - MA</t>
+          <t>Endereço não localizado, Jardim Eldorado (Turú), São Luís - MA</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>São Luís</t>
+          <t>Jardim Eldorado</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Médio-alto</t>
+          <t>Médio</t>
         </is>
       </c>
       <c r="G46" s="6" t="n"/>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>06/2023</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
@@ -4640,71 +4640,81 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
-      <c r="L46" s="8" t="n"/>
+      <c r="J46" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>136</v>
+      </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>2D; 3D</t>
-        </is>
-      </c>
-      <c r="N46" s="9" t="n"/>
-      <c r="O46" s="9" t="n"/>
-      <c r="P46" s="9" t="n"/>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>906870</v>
+      </c>
+      <c r="O46" s="9" t="n">
+        <v>906870</v>
+      </c>
+      <c r="P46" s="9" t="n">
+        <v>6668.161764705882</v>
+      </c>
       <c r="Q46" s="9" t="n"/>
-      <c r="R46" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="R46" s="10" t="n"/>
       <c r="S46" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>agregador</t>
         </is>
       </c>
       <c r="T46" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U46" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>interno</t>
         </is>
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>https://monteplanengenharia.com.br/empreendimentos/edificio-sanpaolo/</t>
+          <t>https://www.imovelnacidade.com/destaque/mb-construtora/</t>
         </is>
       </c>
       <c r="W46" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="X46" s="7" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 2-3Q. 2Q (2 suítes, 1 reversível) ou 3Q (1 suíte). 'Todas as unidades vendidas' (Facebook out/2025).</t>
+          <t>Tipologia detalhada: 3Q casas duplex. DOM Incorporação com MB Engenharia como sócia (empreendimento conjunto). Lançamento 06/2023 confirmado internamente. Casa duplex 3Q, 136m², R$906.870. Produto horizontal Eldorado/Turú. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="47" ht="52" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Monteplan</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Quartier 22</t>
+          <t>Edifício Sanpaolo</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, São Luís - MA</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>São Luís</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -4714,69 +4724,53 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Luxo</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>30</v>
-      </c>
+          <t>Médio-alto</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="n"/>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>09/2022 ⚠ T-36</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>09/2025</t>
-        </is>
-      </c>
-      <c r="J47" s="14" t="n">
-        <v>165</v>
-      </c>
-      <c r="K47" s="14" t="n">
-        <v>165</v>
-      </c>
-      <c r="L47" s="14" t="n">
-        <v>165</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="n"/>
+      <c r="K47" s="14" t="n"/>
+      <c r="L47" s="14" t="n"/>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>3D</t>
-        </is>
-      </c>
-      <c r="N47" s="15" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="O47" s="15" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="P47" s="15" t="n">
-        <v>18181.81818181818</v>
-      </c>
-      <c r="Q47" s="15" t="n">
-        <v>90000000</v>
-      </c>
+          <t>2D; 3D</t>
+        </is>
+      </c>
+      <c r="N47" s="15" t="n"/>
+      <c r="O47" s="15" t="n"/>
+      <c r="P47" s="15" t="n"/>
+      <c r="Q47" s="15" t="n"/>
       <c r="R47" s="16" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="S47" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="T47" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="U47" s="12" t="inlineStr">
         <is>
-          <t>estimativa_T-36</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="V47" s="12" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://monteplanengenharia.com.br/empreendimentos/edificio-sanpaolo/</t>
         </is>
       </c>
       <c r="W47" s="12" t="inlineStr">
@@ -4786,29 +4780,29 @@
       </c>
       <c r="X47" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 3 suítes. Entrega iminente. 1 apto (601) de 30 à venda. ≈97% vendido.</t>
+          <t>Tipologia detalhada: 2-3Q. 2Q (2 suítes, 1 reversível) ou 3Q (1 suíte). 'Todas as unidades vendidas' (Facebook out/2025).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="52" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Monteplan</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Residencial Novo Anil</t>
+          <t>Quartier 22</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Rua Estevão Braga, Cohab Anil IV, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Cohab Anil IV</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -4818,100 +4812,106 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="n"/>
+          <t>Luxo</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>01/2022</t>
+          <t>09/2022 ⚠ T-36</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Pronto</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>53.94</v>
+        <v>165</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>53.94</v>
+        <v>165</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>53.94</v>
+        <v>165</v>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3D</t>
         </is>
       </c>
       <c r="N48" s="9" t="n">
-        <v>324142</v>
+        <v>3000000</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>324142</v>
+        <v>3000000</v>
       </c>
       <c r="P48" s="9" t="n">
-        <v>6009.306637004079</v>
-      </c>
-      <c r="Q48" s="9" t="n"/>
-      <c r="R48" s="10" t="n"/>
+        <v>18181.81818181818</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="R48" s="10" t="n">
+        <v>0.9666666666666667</v>
+      </c>
       <c r="S48" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="T48" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U48" s="6" t="inlineStr">
         <is>
-          <t>memorial</t>
+          <t>estimativa_T-36</t>
         </is>
       </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>https://monteplanengenharia.com.br</t>
+          <t>https://www.delman.com.br</t>
         </is>
       </c>
       <c r="W48" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="X48" s="7" t="inlineStr">
         <is>
-          <t>OBRA CONCLUÍDA (Monteplan, Cohab Anil IV). 32 unid listadas, todas ~R$ 324.142 (área 53,94 m²). R$/m² uniforme R$ 6.009. Padrão popular. SFH 60%. VGV residual listado R$ 10,4M. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tipologia detalhada: 3 suítes. Entrega iminente. 1 apto (601) de 30 à venda. ≈97% vendido.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="52" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>Sá Cavalcante</t>
+          <t>Monteplan</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Ilha Parque Residence</t>
+          <t>Residencial Novo Anil</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Maranhão Novo, São Luís - MA</t>
+          <t>Rua Estevão Braga, Cohab Anil IV, São Luís - MA</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Maranhão Novo</t>
+          <t>Cohab Anil IV</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -4919,88 +4919,92 @@
           <t>Médio</t>
         </is>
       </c>
-      <c r="G49" s="12" t="n">
-        <v>120</v>
-      </c>
+      <c r="G49" s="12" t="n"/>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>02/2019</t>
+          <t>01/2022</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Entregue</t>
+          <t>Pronto</t>
         </is>
       </c>
       <c r="J49" s="14" t="n">
-        <v>64</v>
+        <v>53.94</v>
       </c>
       <c r="K49" s="14" t="n">
-        <v>85</v>
+        <v>53.94</v>
       </c>
       <c r="L49" s="14" t="n">
-        <v>74.5</v>
+        <v>53.94</v>
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>2D; 3D</t>
-        </is>
-      </c>
-      <c r="N49" s="15" t="n"/>
-      <c r="O49" s="15" t="n"/>
-      <c r="P49" s="15" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="15" t="n">
+        <v>324142</v>
+      </c>
+      <c r="O49" s="15" t="n">
+        <v>324142</v>
+      </c>
+      <c r="P49" s="15" t="n">
+        <v>6009.306637004079</v>
+      </c>
       <c r="Q49" s="15" t="n"/>
       <c r="R49" s="16" t="n"/>
       <c r="S49" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="T49" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U49" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>memorial</t>
         </is>
       </c>
       <c r="V49" s="12" t="inlineStr">
         <is>
-          <t>https://www.sacavalcante.com.br</t>
+          <t>https://monteplanengenharia.com.br</t>
         </is>
       </c>
       <c r="W49" s="12" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="X49" s="13" t="inlineStr">
         <is>
-          <t>Tipologia detalhada: 2-3 quartos. 120 aptos (60 2Q + 60 3Q), 12/andar, 15 pavs. Pronto p/ morar. Ao lado do Shopping da Ilha.</t>
+          <t>OBRA CONCLUÍDA (Monteplan, Cohab Anil IV). 32 unid listadas, todas ~R$ 324.142 (área 53,94 m²). R$/m² uniforme R$ 6.009. Padrão popular. SFH 60%. VGV residual listado R$ 10,4M. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="50" ht="52" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Castelucci</t>
+          <t>Sá Cavalcante</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Residencial Ana Vitória</t>
+          <t>Ilha Parque Residence</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Araçagy, São Luís - MA</t>
+          <t>Endereço não localizado, Maranhão Novo, São Luís - MA</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Araçagy</t>
+          <t>Maranhão Novo</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -5010,23 +5014,31 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="n"/>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>120</v>
+      </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>01/2018</t>
+          <t>02/2019</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
-      <c r="L50" s="8" t="n"/>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="K50" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
           <t>2D; 3D</t>
@@ -5039,55 +5051,141 @@
       <c r="R50" s="10" t="n"/>
       <c r="S50" s="6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T50" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U50" s="6" t="inlineStr">
+        <is>
           <t>site_oficial</t>
         </is>
       </c>
-      <c r="T50" s="6" t="inlineStr">
+      <c r="V50" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sacavalcante.com.br</t>
+        </is>
+      </c>
+      <c r="W50" s="6" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="X50" s="7" t="inlineStr">
+        <is>
+          <t>Tipologia detalhada: 2-3 quartos. 120 aptos (60 2Q + 60 3Q), 12/andar, 15 pavs. Pronto p/ morar. Ao lado do Shopping da Ilha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="52" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Castelucci</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Residencial Ana Vitória</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>Endereço não localizado, Araçagy, São Luís - MA</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Araçagy</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="n"/>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>01/2018</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="n"/>
+      <c r="K51" s="14" t="n"/>
+      <c r="L51" s="14" t="n"/>
+      <c r="M51" s="13" t="inlineStr">
+        <is>
+          <t>2D; 3D</t>
+        </is>
+      </c>
+      <c r="N51" s="15" t="n"/>
+      <c r="O51" s="15" t="n"/>
+      <c r="P51" s="15" t="n"/>
+      <c r="Q51" s="15" t="n"/>
+      <c r="R51" s="16" t="n"/>
+      <c r="S51" s="12" t="inlineStr">
+        <is>
+          <t>site_oficial</t>
+        </is>
+      </c>
+      <c r="T51" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="U50" s="6" t="inlineStr">
+      <c r="U51" s="12" t="inlineStr">
         <is>
           <t>site_oficial</t>
         </is>
       </c>
-      <c r="V50" s="6" t="inlineStr">
+      <c r="V51" s="12" t="inlineStr">
         <is>
           <t>https://construtoracastelucci.com.br</t>
         </is>
       </c>
-      <c r="W50" s="6" t="inlineStr">
+      <c r="W51" s="12" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="X50" s="7" t="inlineStr">
+      <c r="X51" s="13" t="inlineStr">
         <is>
           <t>Tipologia detalhada: 2-3Q. Apartamentos 2-3Q Araçagy. Site oficial Castelucci.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="50" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
+    <row r="52" ht="50" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>ESTOQUE — 🟢 ≤15% (últimas unidades) | 🟡 15-40% (em absorção) | 🔴 &gt;40% (estoque amplo).    STATUS = comercial (não físico).    SEGMENTO = classificado pelo R$/m² calculado (ver §4.2 do PADRAO.md).    ⚠ T-36 = lançamento estimado por Entrega−42 meses. Substituir assim que tiver fonte.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>DOM Incorporação  •  Inteligência de Mercado  •  Planilha Mestre v6.3 (Fase 1)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:X50"/>
+  <autoFilter ref="A5:X51"/>
   <mergeCells count="4">
     <mergeCell ref="A52:X52"/>
     <mergeCell ref="D2:X2"/>
-    <mergeCell ref="A51:X51"/>
+    <mergeCell ref="A53:X53"/>
     <mergeCell ref="D3:X3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5907,7 +6005,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="15" t="n">
         <v>0</v>
@@ -5923,19 +6021,19 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Médio</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>Santo Amaro, São Luís</t>
+          <t>Calhau, Santo Amaro, São Luís</t>
         </is>
       </c>
       <c r="I17" s="15" t="n">
-        <v>0</v>
+        <v>3525000</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0</v>
+        <v>6211.453744493392</v>
       </c>
       <c r="K17" s="20" t="n">
         <v>0</v>
